--- a/outputs/evaluation/decision/v1/CF_M05/run_3/CF_M05_decision_eval_llm_report.xlsx
+++ b/outputs/evaluation/decision/v1/CF_M05/run_3/CF_M05_decision_eval_llm_report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,37 +471,37 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AD_06</t>
+          <t>AD_01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Angular applies the MVVM pattern, as its architecture is based on components and services, which is designed for the implementation of user interfaces.</t>
+          <t>En el present projecte, el client s’ha desenvolupat amb Angular, implementant una Single-Page Application (SPA) [19] que renderitza vistes dinàmiques i gestiona la navegació interna sense haver de recarregar la pàgina, millorant la fluïdesa d’ús.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>C_02</t>
+          <t>R_42, C_05</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>P_03</t>
+          <t>AU_13, AU_22, P_03</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>60, 61</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>11a. Usability</t>
+          <t>Temps de resposta no ha superar 1 segon en el 95% de les consultes.; 12a. Speed and latency</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>MVVM</t>
+          <t>Angular; AU_22; MVVM</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -515,7 +515,157 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0.726</v>
+        <v>0.6991000000000001</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>AD_02</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Pel servidor s’ha utilitzat Spring Boot, que proporciona una plataforma per exposar una API REST [20].</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>C_05, C_06, C_09</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>AU_14, P_04</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>12a. Speed and latency; 12a. Availability; 15b. Integrity</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Spring Boot; Layered Architecture</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>CF_M05_AD06</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>The use of this type of architecture allows high scalability, availability and accessibility, since resource management can be done according to needs and anywhere with an Internet connection. It also reduces maintainability, managed by resource providers, and without major expenses, since you pay for the resources consumed.</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>0.6472</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>AD_03</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Pel desplegament de l’aplicació s’ha fetús d’Amazon EKS, un servei que ofereix AWS el qual permet utilitzar Kubernetes (K8s), una plataforma d’orquestració de contenidors creada per Google, sense necessitat d’instal·lar-la ni mantenir-la.</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>R_43, R_44, R_45, R_46, C_06, C_07</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>AU_17, AU_18, AU_19</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>L’aplicació web ha de garantir un funcionament continu i estable, assegurant la seva disponibilitat en qualsevol moment.; La disponibilitat del sistema ha de ser de mínim 99,9%, fins i tot durant els moments d’ús intensiu.; L’aplicació web ha de suportar un gran nombre d’usuaris simultanis sense degradar el seu rendiment.; 12a. Availability; 12f. Capacity</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Amazon Web Services (AWS); Amazon EKS; Kubernetes</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>CF_M05_AD06</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>The use of this type of architecture allows high scalability, availability and accessibility, since resource management can be done according to needs and anywhere with an Internet connection. It also reduces maintainability, managed by resource providers, and without major expenses, since you pay for the resources consumed.</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>0.6856</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>AD_04</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>AWS és una plataforma cloud consolidada amb serveis robustos i una infraestructura fiable. Un dels grans avantatges d’AWS és que disposa d’una selecció molt àmplia de serveis: des del desplegament de servidors i bases de dades, fins a IA, emmagatzematge, seguretat i serveis específics per sectors. Aquesta diversitat fa que sigui fàcil adaptar-se a les necessitats del projecte, permet créixer i escalar el projecte de manera àgil i elimina la necessitat de buscar altre plataformes quan els requisits evolucionen. Per això s’ha triat AWS en comptes d’altres opcions com Google Cloud Platform o Microsoft Azure. El fet de disposar de tants serveis disponibles deixa centrar l’esforç en el desenvolupament de la solució, sense haver d’invertir temps extra en qüestions d’infraestructura. Una altra raó per la qual es va triar AWS va ser que aquesta plataforma inverteix molt en seguretat i certificacions, gestiona múltiples nivells de seguretat i ofereix eines per protegir dades i infraestructures facilitant el compliment de normatives legals i estàndards internacionals.</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Low price and previous company use</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>AU_17</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Low price and previous company use</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Amazon Web Services (AWS)</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>CF_M05_AD06</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>The use of this type of architecture allows high scalability, availability and accessibility, since resource management can be done according to needs and anywhere with an Internet connection. It also reduces maintainability, managed by resource providers, and without major expenses, since you pay for the resources consumed.</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>0.6961000000000001</v>
       </c>
     </row>
   </sheetData>
